--- a/docs/요구사항 정의서_6기_(김네장).xlsx
+++ b/docs/요구사항 정의서_6기_(김네장).xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -981,7 +981,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>범위 밖 연령은 예측을 생성하지 않고 사유를 안내. 적용 연령은 모델 문서와 일치.</t>
+          <t>범위 밖 연령은 예측을 생성하지 않고 사유를 안내. 적용 연령은 모델 문서와 일치. 연령으로 가입을 막지 않으며, 범위 밖 사용자도 챌린지·대시보드·기록은 그대로 이용한다. 빠지는 것은 위험 예측 기능뿐이다.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4888,6 +4888,73 @@
       <c r="M66" s="2" t="inlineStr">
         <is>
           <t>김혜림</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>REQ-CONSENT-003</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>동의·약관</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>법정대리인</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>만 14세 미만</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>동의 확인</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>만 14세 미만 사용자는 법정대리인의 동의를 받아야 서비스 이용을 시작할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>생년월일로 만 14세 미만을 판별해 법정대리인 동의 단계를 노출. 법정대리인 동의 여부와 시각을 저장. 미동의 상태에서는 건강정보 입력 API 403. 동의 확인용으로 수집한 법정대리인 정보는 동의 목적 외로 쓰지 않으며, 동의가 확인되지 않으면 수집일로부터 5일 이내 파기. 근거: 개인정보보호법 제22조의2.</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>W02</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>김혜림</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>김이슬</t>
         </is>
       </c>
     </row>
@@ -4986,7 +5053,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>REQ-USER-001,002,004 / REQ-CONSENT-001</t>
+          <t>REQ-USER-001,002,004 / REQ-CONSENT-001,003 / NFR-SEC-003</t>
         </is>
       </c>
     </row>
@@ -5013,7 +5080,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>REQ-ELIG-001~004</t>
+          <t>REQ-ELIG-001,002,003,004</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5107,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>REQ-HEALTH-001~004</t>
+          <t>REQ-HEALTH-001,002,003,004 / NFR-SEC-003</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5161,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>REQ-PRED-001,003 / REQ-RECO-001 / NFR-SAFE-001~003</t>
+          <t>REQ-PRED-001,003,006 / REQ-RECO-001 / NFR-SAFE-001,002,003</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5215,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>REQ-PRED-004 / REQ-DASH-001,004,005</t>
+          <t>REQ-PRED-004,007 / REQ-DASH-001,004,005 / NFR-SAFE-001</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5242,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>REQ-CHAL-001~003</t>
+          <t>REQ-CHAL-001,002,003</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5269,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>REQ-CHAL-004~006 / REQ-RECO-002</t>
+          <t>REQ-CHAL-004,005,006,007 / REQ-RECO-002</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5296,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>REQ-DASH-002,003 / REQ-HEALTH-004</t>
+          <t>REQ-DASH-002,003</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5323,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>REQ-FEED-001 / REQ-NOTI-001 / REQ-CONSENT-002 / REQ-USER-003</t>
+          <t>REQ-USER-003 / REQ-CONSENT-002 / REQ-NOTI-001 / REQ-FEED-001</t>
         </is>
       </c>
     </row>

--- a/docs/요구사항 정의서_6기_(김네장).xlsx
+++ b/docs/요구사항 정의서_6기_(김네장).xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -477,6 +477,7 @@
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -510,6 +511,11 @@
           <t>수정자</t>
         </is>
       </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -638,6 +644,11 @@
           <t>김혜성</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>이슬님 버전과 통합되며 대체됨 — 최종 위험 범주는 저위험/경계/고위험(화면 표기: 정상/주의/위험)으로 확정 (REQ-PRED-001, 이슬님 버전 기준)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -702,6 +713,11 @@
           <t>김혜성</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>이슬님 버전과 통합되며 대체됨 — 혈관 나이 요구사항은 REQ-DASH-006이 아닌 REQ-PRED-006으로 통합 (카테고리: 추적 대시보드 → 예측·분석)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -732,6 +748,11 @@
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>김혜성</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>이슬님 버전과 통합되며 대체됨 — 최종 REQ-RECO-002는 "구성 분석 결과 확인"으로 단순화, 부족 영양소 분석 상세는 제외</t>
         </is>
       </c>
     </row>
@@ -810,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1340,7 +1361,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>범위 밖 연령은 예측을 생성하지 않고 사유를 안내. 적용 연령은 모델 문서와 일치.</t>
+          <t>범위 밖 연령은 예측을 생성하지 않고 사유를 안내. 적용 연령은 모델 문서와 일치. 연령으로 가입을 막지 않으며, 범위 밖 사용자도 챌린지·대시보드·기록은 그대로 이용한다. 빠지는 것은 위험 예측 기능뿐이다.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1660,7 +1681,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>사용자는 신체계측(신장·체중·허리둘레), 혈압, 공복혈당, 흡연·음주·운동, 가족력 등 고혈압 위험 예측에 필요한 건강정보를 입력할 수 있어야 한다.</t>
+          <t>사용자는 위험 예측 모델에 필요한 건강정보를 입력할 수 있어야 한다. 필수 항목은 나이·성별·수축기혈압·이완기혈압·신장·체중·흡연 여부·당뇨병 여부·부모 고혈압 가족력이며, 선택 항목은 총콜레스테롤·HDL콜레스테롤·음주 빈도·운동 빈도이다.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1675,7 +1696,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>필수·선택 항목과 단위를 구분. 입력 계약을 스키마 버전으로 추적. 공복혈당은 진단 확정치가 아닌 참고 입력값으로 취급한다.</t>
+          <t>필수·선택 항목과 단위를 구분(혈압 mmHg, 신장 cm, 체중 kg, 콜레스테롤 mg/dL). BMI는 신장·체중에서 서버가 계산하며 사용자가 직접 입력하지 않는다. 선택 항목이 비어도 예측은 수행하되 결과에 정확도 한계를 표시. 입력 계약을 스키마 버전으로 추적.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1841,7 +1862,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>AI 예측</t>
+          <t>예측·분석</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1861,7 +1882,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>사용자는 입력한 건강정보를 기반으로 고혈압 위험 선별 결과를 확인할 수 있어야 한다.</t>
+          <t>사용자는 입력한 건강정보를 기반으로 만성질환 위험 선별 결과를 확인할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1876,7 +1897,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>결과는 진단이 아닌 선별 정보. 위험 범주는 낮음/주의/높음 3단계로 표시.</t>
+          <t>결과는 진단이 아닌 선별 정보. 위험 범주는 저위험·경계·고위험 3단계로 구분한다. 저위험은 추가 안내 없음, 경계는 기여 요인과 챌린지를 함께 제시, 고위험은 REQ-PRED-005(검사·상담 안내)로 연결한다. 화면 문구는 정상·주의·위험으로 표기하며 3단계와 1:1 대응한다.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1908,7 +1929,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>AI 예측</t>
+          <t>예측·분석</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1975,7 +1996,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>AI 예측</t>
+          <t>예측·분석</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2042,7 +2063,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>AI 예측</t>
+          <t>예측·분석</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2109,7 +2130,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>AI 예측</t>
+          <t>예측·분석</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2263,7 +2284,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>사용자는 정해진 주기 단위의 챌린지 사이클을 시작할 수 있어야 한다.</t>
+          <t>사용자는 4주 단위의 챌린지 사이클을 시작할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2278,7 +2299,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>사이클 시작일·종료일 저장. 진행 중 사이클은 1개로 제한. 사이클 주기는 4주.</t>
+          <t>사이클 시작일·종료일 저장. 진행 중 사이클은 1개로 제한. 기본 주기는 4주. 데모 시연은 사이클을 줄이지 않고 테스트 계정에 완주 이력을 미리 채워 대응한다.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2330,7 +2351,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>사용자는 제시된 후보 중 수행할 챌린지를 선택하고 목표 횟수를 설정할 수 있어야 한다.</t>
+          <t>사용자는 추천된 챌린지 후보 중 하나를 선택해 사이클을 시작할 수 있어야 한다. 후보는 집밥·저염식, 나트륨 섭취 기록, 아침 식사, 저염 외식 요령 4종을 기본으로 한다.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2345,7 +2366,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>선택 시점의 챌린지 정의를 스냅샷으로 저장.</t>
+          <t>후보는 최소 3개 제시. 각 후보에 연결된 위험 요인을 함께 표시. 후보 목록은 문제정의서의 근거 기반 챌린지 소재와 일치해야 한다.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -3000,7 +3021,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>사용자는 식단 사진을 올려 음식 구성과 개인별 부족 영양소를 분석하고, 개선 피드백을 확인할 수 있어야 한다.</t>
+          <t>사용자는 식단 사진을 올려 구성 분석 결과를 확인할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3015,7 +3036,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>분석 실패 시 사용자 수동 입력으로 대체 가능. 부족 영양소 항목과 개선 방향을 함께 제시한다.</t>
+          <t>분석 실패 시 사용자 수동 입력으로 대체 가능.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -5052,32 +5073,32 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>REQ-DASH-006</t>
+          <t>REQ-PRED-006</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>추적 대시보드</t>
+          <t>예측·분석</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
+          <t>결과 표현</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
           <t>혈관 나이</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>위험 프로필 나이</t>
-        </is>
-      </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>추정 계산</t>
+          <t>나이 환산</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>사용자는 예측 모델 결과를 기반으로 실제 나이 대비 추정 혈관 나이를 확인할 수 있어야 한다.</t>
+          <t>사용자는 위험 점수를 실제 나이와 비교할 수 있는 혈관 나이로 확인할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -5092,12 +5113,12 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>혈관 나이는 진단 확정치가 아닌 추정치임을 함께 표시. 실제 나이 대비 차이를 색상+기호로 표시.</t>
+          <t>위험 점수를 동일 위험도의 평균 연령으로 환산해 표시. 실제 나이와의 차이를 함께 제시. 진단적 표현을 쓰지 않으며 NFR-SAFE-001을 따른다. 추정치임을 함께 표기.</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>W08</t>
+          <t>W06</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5119,32 +5140,32 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>REQ-NOTI-002</t>
+          <t>REQ-PRED-007</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>예측·분석</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>리마인더</t>
+          <t>재예측</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>건강정보 입력</t>
+          <t>실행 시점</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>발송</t>
+          <t>자동 트리거</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>사용자는 건강정보 재입력(재검진) 시점에 알림을 받을 수 있어야 한다.</t>
+          <t>챌린지 사이클이 종료되면 최신 건강정보로 재예측이 자동 실행되고 결과가 대시보드에 반영되어야 한다.</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -5154,17 +5175,17 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>낮음</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>사용자별 알림 수신 설정을 따르며 미설정 시 발송하지 않는다.</t>
+          <t>사이클 종료 시 자동 실행. 사용자가 수동으로 재예측을 요청할 수도 있으며 요청 간 최소 간격은 7일. 재예측 결과는 기존 결과를 덮어쓰지 않고 이력으로 쌓여 REQ-DASH-002에서 조회된다.</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W08</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5174,77 +5195,278 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>김효민</t>
+          <t>김혜성</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>김혜림</t>
+          <t>김이슬</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>REQ-CHAL-007</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>중단</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>포기·미달</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>재도전 유도</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>사용자는 진행 중인 사이클을 중단할 수 있고, 목표 미달로 종료된 경우 다음 행동을 안내받아야 한다.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>중단 시 사유를 선택적으로 수집. 중단·미달 사이클도 이력에 남긴다. 종료 시 달성률에 따라 재도전 또는 목표 조정을 제안. 실패를 질책하는 표현을 쓰지 않는다.</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>김이슬</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>김혜림</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>REQ-CONSENT-003</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>동의·약관</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>법정대리인</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>만 14세 미만</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>동의 확인</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>만 14세 미만 사용자는 법정대리인의 동의를 받아야 서비스 이용을 시작할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>생년월일로 만 14세 미만을 판별해 법정대리인 동의 단계를 노출. 법정대리인 동의 여부와 시각을 저장. 미동의 상태에서는 건강정보 입력 API 403. 동의 확인용으로 수집한 법정대리인 정보는 동의 목적 외로 쓰지 않으며, 동의가 확인되지 않으면 수집일로부터 5일 이내 파기. 근거: 개인정보보호법 제22조의2.</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>W02</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>김혜림</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>김이슬</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>REQ-NOTI-002</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>알림</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>리마인더</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>건강정보 입력</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>발송</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>사용자는 건강정보 재입력(재검진) 시점에 알림을 받을 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>사용자별 알림 수신 설정을 따르며 미설정 시 발송하지 않는다.</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>김효민</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>김혜림</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
           <t>REQ-NOTI-003</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>리마인더</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>예방행동가이드 확인</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>발송</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>사용자는 새로 생성된 예방 행동 제안(LLM 추천)을 확인하라는 알림을 받을 수 있어야 한다.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>낮음</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>사용자별 알림 수신 설정을 따르며 미설정 시 발송하지 않는다.</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>W12</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>김효민</t>
         </is>
       </c>
-      <c r="M66" s="2" t="inlineStr">
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t>김혜림</t>
         </is>
@@ -5345,7 +5567,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>REQ-USER-001,002,004 / REQ-CONSENT-001</t>
+          <t>REQ-USER-001,002,004 / REQ-CONSENT-001,003 / NFR-SEC-003</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>REQ-ELIG-001~004</t>
+          <t>REQ-ELIG-001,002,003,004</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5621,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>REQ-HEALTH-001~004</t>
+          <t>REQ-HEALTH-001,002,003,004 / NFR-SEC-003</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5675,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>REQ-PRED-001,003 / REQ-RECO-001 / NFR-SAFE-001~003</t>
+          <t>REQ-PRED-001,003,006 / REQ-RECO-001 / NFR-SAFE-001,002,003</t>
         </is>
       </c>
     </row>
@@ -5502,12 +5724,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>하단 탭, 최신 위험도 카드, 오늘의 챌린지 진행률, 사이클 현황, 빈 상태 CTA, 혈관 나이 카드</t>
+          <t>하단 탭, 최신 위험도 카드, 오늘의 챌린지 진행률, 사이클 현황, 빈 상태 CTA</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>REQ-PRED-004 / REQ-DASH-001,004,005 / REQ-DASH-006</t>
+          <t>REQ-PRED-004,007 / REQ-DASH-001,004,005 / NFR-SAFE-001</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5756,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>REQ-CHAL-001~003</t>
+          <t>REQ-CHAL-001,002,003</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5783,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>REQ-CHAL-004~006 / REQ-RECO-002</t>
+          <t>REQ-CHAL-004,005,006,007 / REQ-RECO-002</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5810,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>REQ-DASH-002,003 / REQ-HEALTH-004</t>
+          <t>REQ-DASH-002,003</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5837,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>REQ-FEED-001 / REQ-NOTI-001 / REQ-CONSENT-002 / REQ-USER-003</t>
+          <t>REQ-USER-003 / REQ-CONSENT-002 / REQ-NOTI-001 / REQ-FEED-001</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6328,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>문제정의서(docs/문제정의서_PAEON.md), 통계·문헌 출처, 페르소나</t>
+          <t>문제정의서, 통계·문헌 출처, 페르소나</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">

--- a/docs/요구사항 정의서_6기_(김네장).xlsx
+++ b/docs/요구사항 정의서_6기_(김네장).xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -815,6 +815,38 @@
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>개정이력 탭 없음, REQ-NOTI-002/003 없음, REQ-PRED Category "AI 예측"/"예측·분석" 혼재</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>이슬님 브랜치 버전을 베이스로 병합: ① 개정이력 탭 통합 ② REQ-NOTI-002(건강정보 재입력 알림)·REQ-NOTI-003(예방행동가이드 확인 알림) 추가 ③ REQ-PRED-001~005 Category를 "예측·분석"으로 통일</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>이슬님 브랜치(PR #2)와 혜성님 브랜치가 같은 파일을 독립적으로 수정해 발생한 차이를 병합 — 충돌 없이 양쪽 작업 내용을 모두 보존</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>김혜성</t>
         </is>

--- a/docs/요구사항 정의서_6기_(김네장).xlsx
+++ b/docs/요구사항 정의서_6기_(김네장).xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +42,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="001155CC"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -102,6 +106,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -852,6 +859,70 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>REQ-PRED-001 수용기준에 위험단계 색상 표시 없음 / REQ-PRED-003이 전체 요인 나열로 정의됨 / 나트륨 설문·라벨 재정의·챌린지 피처검증 요구사항 없음</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>① REQ-PRED-001 수용기준에 "위험 단계는 색상(정상=초록/주의=노랑/위험=빨강)으로 표시" 추가 ② REQ-PRED-003을 "1위 기여요인만 강조"로 변경 ③ REQ-PRED-008(나트륨 5문항 설문→점수→등급→모델입력) 신규 ④ REQ-PRED-009(정상 vs 경계군 이진분류, 고혈압은 예측 제외) 신규 ⑤ NFR-ML-006(챌린지 피처는 상관관계 검증된 것만 채택) 신규</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23 회의록 결정사항 반영 + KNHANES 이용지침서 원문 대조로 확인된 HE_HP 4단계 코드 구조 반영</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>REQ-PRED-003 방향 미명시 / REQ-PRED-009와 REQ-ELIG-002 기준 충돌 / NFR-ML-006 임계값 없음 / NFR-ML-001,003 구체 기준 없음 / 모델 이원화·학습모집단 정의 요구사항 없음</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>① REQ-PRED-003: "위험 증가 방향 1위 요인"으로 한정 ② REQ-PRED-009: 라벨 정의로 범위 축소하고 REQ-ELIG-002(자기보고)와 학습모집단필터(NFR-ML-008)를 명확히 분리 ③ NFR-ML-006: SHAP상위5위 또는 상관계수 0.1 이상 기준 추가 ④ NFR-ML-001: 결측코드(8/9) 구분처리 원칙 추가 ⑤ NFR-ML-003: AUC-ROC 기본지표 + 비교모델 명시 ⑥ NFR-ML-007(신규): 모델A/B 이원화 및 데이터셋 출처 명시 ⑦ NFR-ML-008(신규): 모델B 학습 모집단(정상+경계군) 정의, 평가기준표 3-1에 NFR-ML-006~008 연결 추가</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>모델/예측·분석 영역 자체 검토 중 발견한 설계 충돌 및 평가기준(3-1) 증빙 요건 미비 보완</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -863,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1929,7 +2000,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>결과는 진단이 아닌 선별 정보. 위험 범주는 저위험·경계·고위험 3단계로 구분한다. 저위험은 추가 안내 없음, 경계는 기여 요인과 챌린지를 함께 제시, 고위험은 REQ-PRED-005(검사·상담 안내)로 연결한다. 화면 문구는 정상·주의·위험으로 표기하며 3단계와 1:1 대응한다.</t>
+          <t>결과는 진단이 아닌 선별 정보. 위험 범주는 저위험·경계·고위험 3단계로 구분한다. 저위험은 추가 안내 없음, 경계는 기여 요인과 챌린지를 함께 제시, 고위험은 REQ-PRED-005(검사·상담 안내)로 연결한다. 화면 문구는 정상·주의·위험으로 표기하며 3단계와 1:1 대응한다. 위험 단계는 색상(정상=초록/주의=노랑/위험=빨강)으로 함께 표시한다.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2063,7 +2134,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>요인별 영향 방향과 중요도를 표시. 개선 가능 요인은 챌린지로 연결.</t>
+          <t>위험을 높이는 방향(양의 기여도)의 요인 중 1위만 강조해 표시한다. 위험을 낮추는 방향(음의 기여도)의 요인은 강조 표시하지 않는다. 개선 가능 요인은 챌린지로 연결.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4408,7 +4479,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>스케일러·인코더를 학습 셋에만 fit. 분리 코드로 증빙.</t>
+          <t>스케일러·인코더를 학습 셋에만 fit. 분리 코드로 증빙. 결측 코드는 변수별 의미에 따라 구분 처리한다(예: 8=비해당·해당 범주 유지, 9=모름/무응답만 결측 처리) — 임의로 통합 처리하지 않는다.</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -4542,7 +4613,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>실험표·혼동행렬·개선 전후 결과를 제출.</t>
+          <t>평가지표는 AUC-ROC를 기본으로 하고 F1-score·혼동행렬을 함께 기록한다. 로지스틱회귀(베이스라인)와 트리 계열 모델(XGBoost 또는 LightGBM) 최소 2종을 동일 조건에서 비교한다. 실험표·혼동행렬·개선 전후 결과를 제출.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -5499,6 +5570,341 @@
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>김혜림</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PRED-008</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>결과 입력</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>나트륨 설문</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>점수화</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>사용자는 나트륨 섭취 수준을 5문항 설문으로 응답하고, 그 응답이 점수화·등급화되어 모델 B의 나트륨 섭취 피처로 반영되어야 한다.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>5개 문항(국물·김치·면류·절임·양념) 각 0~2점, 합산 0~10점. 0~3점=하(≤2,088mg), 4~6점=중(2,088~3,363mg), 7~10점=상(&gt;3,363mg)으로 매핑해 모델 B 입력값으로 사용한다. 등급 컷은 KNHANES 2022-2024 병합 데이터의 나트륨 섭취량 실측 삼분위수 기준이다.</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>W04</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>김이슬</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PRED-009</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>위험 예측</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>대상군 정의</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>경계군 분류</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>모델 B의 라벨은 정상(0) vs 경계군(1, 주의혈압·고혈압전단계)의 이진 분류로 정의한다. 학습 데이터 모집단 구성은 NFR-ML-007을 따른다.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>라벨은 정상(0)/경계군(1) 이진값으로 정의한다. 서비스에서 예측 제공 대상자 판단은 REQ-ELIG-002(자기보고 기반 기진단 여부)를 그대로 따르며, 사용자가 입력한 혈압 수치가 고혈압 기준에 해당하더라도 자기보고상 미진단이면 예측을 제공하고 결과가 고위험이면 REQ-PRED-005(검사·상담 안내)로 연결한다. (참고: 학습 데이터에서 HE_HP=4(고혈압) 응답자를 제외하는 것은 훈련 모집단 구성의 문제이며, REQ-ELIG-002의 서비스 시점 자기보고 기준과는 별개다 — NFR-ML-007 참고)</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>W06</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>김이슬</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>NFR-ML-006</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>AI 품질</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>챌린지 연계</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>피처 유의성</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>사전 검증</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>챌린지 후보로 채택되는 생활습관 피처는 학습 데이터에서 라벨과의 상관관계 또는 유의미한 영향력이 사전에 검증된 것이어야 한다.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>피처별 SHAP 중요도 평균(절댓값) 상위 5위 이내이거나, 라벨과의 상관계수 절댓값이 0.1 이상인 피처만 챌린지 후보로 채택한다. 기준 미달 피처는 챌린지 후보에서 제외하거나 참고용으로만 표시한다. 분석 결과는 REQ-CHAL의 고정·선택 미션 분류 근거로 사용한다.</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>김혜림</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>NFR-ML-007</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>AI 품질</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>데이터셋</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>모델 이원화</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>독립 학습</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>모델 A(장기 위험)와 모델 B(현재 위험)는 서로 다른 데이터셋으로 각각 독립적으로 학습하며, 두 데이터를 하나로 합쳐 학습하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>모델 A는 Framingham Heart Study(미국, 코호트, 10년 후 CHD 예측), 모델 B는 국민건강영양조사 2022-2024(한국, 횡단면, 현재 경계군 여부 예측) 데이터셋을 사용한다. 두 모델의 학습 코드·아티팩트(모델 파일·스케일러)는 분리해 관리한다.</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>김혜림</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>NFR-ML-008</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>AI 품질</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>모집단</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>학습 대상</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>고혈압군 제외</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>모델 B의 학습 데이터 모집단은 정상 또는 경계군에 해당하는 응답자로 한정하며, 이미 고혈압(4단계)에 해당하는 응답자는 학습 대상에서 제외한다.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>HE_HP=1(정상), 2·3(경계군)에 해당하는 응답자만 학습에 포함하고, HE_HP=4(고혈압)는 제외한다. 이는 학습 데이터 구성 단계의 필터링이며, 서비스 시점의 사용자 자격 판단(REQ-ELIG-002, 자기보고 기반)과는 별개 기준이다.</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>김혜성</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t>김혜림</t>
         </is>
@@ -6547,7 +6953,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>NFR-ML-001~003</t>
+          <t>NFR-ML-001~003, NFR-ML-006~008</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
